--- a/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-address.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="241">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T17:40:42+00:00</t>
+    <t>2026-10-20T06:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,26 +351,26 @@
 </t>
   </si>
   <si>
-    <t>Address Municipality Code (Gemeindecode)</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
-  </si>
-  <si>
-    <t>Address.extension:municipalityKey</t>
-  </si>
-  <si>
-    <t>municipalityKey</t>
+    <t>Municipality code (Gemeindecode)</t>
+  </si>
+  <si>
+    <t>The municipality code (Gemeindecode) of the Austrian municipality the address belongs to, as published by Statistics Austria (Statistik Austria). It is generally identical to the Gemeindekennziffer (GKZ), except in Vienna, where the Gemeindecode varies by district while the Gemeindekennziffer is 90001 for the whole city.</t>
+  </si>
+  <si>
+    <t>Address.extension:GKZ</t>
+  </si>
+  <si>
+    <t>GKZ</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityKey}
 </t>
   </si>
   <si>
-    <t>Address Municipality Key (Gemeindekennziffer)</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality key (Gemeindekennziffer) part of the Austrian address. The municipality key is related to the [municipality code (Gemeindecode)](StructureDefinition-at-core-ext-address-municipalityCode.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
+    <t>Gemeindekennziffer (GKZ)</t>
+  </si>
+  <si>
+    <t>The Gemeindekennziffer (GKZ) of the Austrian municipality the address belongs to, as published by Statistics Austria (Statistik Austria). It is generally identical to the municipality code (Gemeindecode), except in Vienna, where the Gemeindekennziffer is 90001 for the whole city while the Gemeindecode varies by district.</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -523,10 +523,10 @@
 </t>
   </si>
   <si>
-    <t>Name of the street</t>
-  </si>
-  <si>
-    <t>Name of the street without the street number</t>
+    <t>Street name (Straßenname)</t>
+  </si>
+  <si>
+    <t>Name of the street (Straßenname) without the street number.</t>
   </si>
   <si>
     <t>ADXP[partType=STR]</t>
@@ -542,10 +542,10 @@
 </t>
   </si>
   <si>
-    <t>Number of the street</t>
-  </si>
-  <si>
-    <t>Number of the street without the street name</t>
+    <t>Street number (Hausnummer)</t>
+  </si>
+  <si>
+    <t>Number of the house (Hausnummer) without the street name.</t>
   </si>
   <si>
     <t>ADXP[partType=BNR]</t>
@@ -561,7 +561,10 @@
 </t>
   </si>
   <si>
-    <t>Floor and/or door number</t>
+    <t>Floor and/or door number (Stiege, Stock, Tür)</t>
+  </si>
+  <si>
+    <t>Additional locator information within a building, such as staircase (Stiege), floor (Stock) and/or door number (Tür).</t>
   </si>
   <si>
     <t>ADXP[partType=ADL]</t>
@@ -577,10 +580,10 @@
 </t>
   </si>
   <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
-    <t>Additional information about the street address</t>
+    <t>Additional address information (Adresszusatz)</t>
+  </si>
+  <si>
+    <t>Additional information about the street address (Adresszusatz), e.g. street direction, P.O. Box number or delivery hints.</t>
   </si>
   <si>
     <t>Address.line.value</t>
@@ -2744,7 +2747,7 @@
         <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2813,7 +2816,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -2824,13 +2827,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>160</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
@@ -2852,13 +2855,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2938,10 +2941,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2967,10 +2970,10 @@
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2994,7 +2997,7 @@
         <v>21</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="X17" t="s" s="2">
         <v>21</v>
@@ -3021,7 +3024,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3050,14 +3053,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3079,10 +3082,10 @@
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3097,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3133,7 +3136,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3148,28 +3151,28 @@
         <v>127</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3191,13 +3194,13 @@
         <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3211,7 +3214,7 @@
         <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3247,7 +3250,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3262,10 +3265,10 @@
         <v>127</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3276,14 +3279,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3305,10 +3308,10 @@
         <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3359,7 +3362,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3374,28 +3377,28 @@
         <v>127</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3417,10 +3420,10 @@
         <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3435,7 +3438,7 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>21</v>
@@ -3471,7 +3474,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3486,24 +3489,24 @@
         <v>127</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3529,13 +3532,13 @@
         <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3585,7 +3588,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3600,24 +3603,24 @@
         <v>127</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3640,17 +3643,17 @@
         <v>117</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3663,7 +3666,7 @@
         <v>21</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U23" t="s" s="2">
         <v>21</v>
@@ -3699,7 +3702,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3714,13 +3717,13 @@
         <v>127</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
